--- a/tables/supplementary_tables.xlsx
+++ b/tables/supplementary_tables.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="1625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="1623">
   <si>
     <t xml:space="preserve">strain</t>
   </si>
@@ -2645,13 +2645,7 @@
     <t xml:space="preserve">sd_avg_sd</t>
   </si>
   <si>
-    <t xml:space="preserve">Redox disruption</t>
-  </si>
-  <si>
     <t xml:space="preserve">MoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other|unknown</t>
   </si>
   <si>
     <t xml:space="preserve">Use</t>
@@ -15220,22 +15214,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1547</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1548</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1549</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1551</v>
       </c>
     </row>
     <row r="2">
@@ -15243,16 +15237,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C2" t="n">
         <v>7.943</v>
       </c>
       <c r="D2" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E2" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="F2" t="n">
         <v>0.98</v>
@@ -15263,16 +15257,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C3" t="n">
         <v>6.201</v>
       </c>
       <c r="D3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E3" t="s">
         <v>1552</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1554</v>
       </c>
       <c r="F3" t="n">
         <v>0.769</v>
@@ -15283,16 +15277,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C4" t="n">
         <v>6.134</v>
       </c>
       <c r="D4" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E4" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="F4" t="n">
         <v>0.818</v>
@@ -15303,16 +15297,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C5" t="n">
         <v>5.914</v>
       </c>
       <c r="D5" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E5" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -15323,16 +15317,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C6" t="n">
         <v>5.869</v>
       </c>
       <c r="D6" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="E6" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -15343,16 +15337,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C7" t="n">
         <v>5.418</v>
       </c>
       <c r="D7" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E7" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -15363,16 +15357,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C8" t="n">
         <v>5.341</v>
       </c>
       <c r="D8" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E8" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="F8" t="n">
         <v>0.805</v>
@@ -15383,16 +15377,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="C9" t="n">
         <v>5.219</v>
       </c>
       <c r="D9" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E9" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="F9" t="n">
         <v>0.583</v>
@@ -15403,16 +15397,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C10" t="n">
         <v>5.206</v>
       </c>
       <c r="D10" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="E10" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="F10" t="n">
         <v>0.349</v>
@@ -15423,16 +15417,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="C11" t="n">
         <v>5.183</v>
       </c>
       <c r="D11" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E11" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -15443,16 +15437,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C12" t="n">
         <v>4.825</v>
       </c>
       <c r="D12" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E12" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="F12" t="n">
         <v>0.636</v>
@@ -15463,16 +15457,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C13" t="n">
         <v>4.782</v>
       </c>
       <c r="D13" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E13" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="F13" t="n">
         <v>0.789</v>
@@ -15483,16 +15477,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="C14" t="n">
         <v>4.742</v>
       </c>
       <c r="D14" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E14" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="F14" t="n">
         <v>0.882</v>
@@ -15503,16 +15497,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="C15" t="n">
         <v>4.694</v>
       </c>
       <c r="D15" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E15" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -15523,16 +15517,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="C16" t="n">
         <v>4.653</v>
       </c>
       <c r="D16" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E16" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="F16" t="n">
         <v>0.693</v>
@@ -15543,16 +15537,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C17" t="n">
         <v>4.527</v>
       </c>
       <c r="D17" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E17" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="F17" t="n">
         <v>0.68</v>
@@ -15563,16 +15557,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="C18" t="n">
         <v>4.5</v>
       </c>
       <c r="D18" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E18" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F18" t="n">
         <v>0.067</v>
@@ -15583,16 +15577,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C19" t="n">
         <v>4.495</v>
       </c>
       <c r="D19" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E19" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="F19" t="n">
         <v>0.965</v>
@@ -15603,16 +15597,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C20" t="n">
         <v>4.423</v>
       </c>
       <c r="D20" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E20" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="F20" t="n">
         <v>0.236</v>
@@ -15623,16 +15617,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C21" t="n">
         <v>4.315</v>
       </c>
       <c r="D21" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E21" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="F21" t="n">
         <v>0.963</v>
@@ -15643,16 +15637,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C22" t="n">
         <v>4.309</v>
       </c>
       <c r="D22" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E22" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="F22" t="n">
         <v>0.554</v>
@@ -15663,16 +15657,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C23" t="n">
         <v>4.267</v>
       </c>
       <c r="D23" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E23" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="F23" t="n">
         <v>0.053</v>
@@ -15696,497 +15690,497 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B2" t="s">
         <v>1381</v>
       </c>
-      <c r="B2" t="s">
-        <v>1383</v>
-      </c>
       <c r="C2" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B3" t="s">
         <v>1230</v>
       </c>
-      <c r="B3" t="s">
-        <v>1232</v>
-      </c>
       <c r="C3" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B4" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C4" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B5" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C5" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B6" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C6" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B7" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C7" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B8" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C8" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B9" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C9" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B10" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C10" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B11" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C11" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B12" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="C12" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B13" t="s">
         <v>1094</v>
       </c>
-      <c r="B13" t="s">
-        <v>1096</v>
-      </c>
       <c r="C13" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B14" t="s">
         <v>1372</v>
       </c>
-      <c r="B14" t="s">
-        <v>1374</v>
-      </c>
       <c r="C14" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>978</v>
+      </c>
+      <c r="B15" t="s">
         <v>980</v>
       </c>
-      <c r="B15" t="s">
-        <v>982</v>
-      </c>
       <c r="C15" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B16" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C16" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B17" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C17" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B18" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C18" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B19" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C19" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B20" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C20" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B21" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C21" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B22" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C22" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B23" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C23" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B24" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C24" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B25" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C25" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B26" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C26" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B27" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C27" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B28" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C28" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B29" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C29" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B30" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C30" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B31" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C31" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B32" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="C32" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B33" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C33" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B34" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C34" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B35" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C35" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B36" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C36" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B37" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C37" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B38" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C38" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B39" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="C39" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B40" t="s">
         <v>1487</v>
       </c>
-      <c r="B40" t="s">
-        <v>1489</v>
-      </c>
       <c r="C40" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B41" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C41" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>998</v>
+      </c>
+      <c r="B42" t="s">
         <v>1000</v>
       </c>
-      <c r="B42" t="s">
-        <v>1002</v>
-      </c>
       <c r="C42" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B43" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="C43" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B44" t="s">
         <v>1330</v>
       </c>
-      <c r="B44" t="s">
-        <v>1332</v>
-      </c>
       <c r="C44" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B45" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C45" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
   </sheetData>
@@ -33394,7 +33388,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="56.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
@@ -33416,113 +33410,153 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B2" t="s">
         <v>869</v>
       </c>
-      <c r="B2" t="s">
-        <v>870</v>
-      </c>
       <c r="C2" t="n">
-        <v>39.1436145540496</v>
+        <v>41.5899948885625</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3755034322355</v>
+        <v>16.4405934906598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="B3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C3" t="n">
-        <v>38.5103766615408</v>
+        <v>41.222455322931</v>
       </c>
       <c r="D3" t="n">
-        <v>17.0772539041566</v>
+        <v>13.6660276396835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>871</v>
+        <v>740</v>
       </c>
       <c r="B4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C4" t="n">
-        <v>32.8150842321718</v>
+        <v>37.5386181981072</v>
       </c>
       <c r="D4" t="n">
-        <v>15.8719373191107</v>
+        <v>7.61854181379301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B5" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C5" t="n">
-        <v>43.8673814506641</v>
+        <v>36.1461903425779</v>
       </c>
       <c r="D5" t="n">
-        <v>16.172497914988</v>
+        <v>17.561921298193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B6" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C6" t="n">
-        <v>38.2067244277064</v>
+        <v>34.4793238260108</v>
       </c>
       <c r="D6" t="n">
-        <v>19.0713555081279</v>
+        <v>17.9189773679303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>695</v>
+        <v>745</v>
       </c>
       <c r="B7" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C7" t="n">
-        <v>33.532642333449</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5.41517963856507</v>
-      </c>
+        <v>19.8697371921976</v>
+      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>784</v>
+        <v>701</v>
       </c>
       <c r="B8" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C8" t="n">
-        <v>31.5251006677374</v>
+        <v>43.8673814506641</v>
       </c>
       <c r="D8" t="n">
-        <v>8.97448401381535</v>
+        <v>16.172497914988</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>708</v>
+      </c>
+      <c r="B9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C9" t="n">
+        <v>38.2067244277064</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19.0713555081279</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>695</v>
+      </c>
+      <c r="B10" t="s">
+        <v>870</v>
+      </c>
+      <c r="C10" t="n">
+        <v>33.532642333449</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.41517963856507</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>784</v>
+      </c>
+      <c r="B11" t="s">
+        <v>870</v>
+      </c>
+      <c r="C11" t="n">
+        <v>31.5251006677374</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.97448401381535</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>726</v>
       </c>
-      <c r="B9" t="s">
-        <v>872</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B12" t="s">
+        <v>870</v>
+      </c>
+      <c r="C12" t="n">
         <v>30.2221600578266</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D12" t="n">
         <v>12.1880216901666</v>
       </c>
     </row>
@@ -33553,28 +33587,28 @@
         <v>683</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>878</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="2">
@@ -33637,7 +33671,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B4" t="s">
         <v>784</v>
@@ -33780,7 +33814,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B9" t="s">
         <v>726</v>
@@ -33923,7 +33957,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B14" t="s">
         <v>695</v>
@@ -34153,7 +34187,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B22" t="s">
         <v>701</v>
@@ -34441,7 +34475,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B32" t="s">
         <v>708</v>
@@ -34488,25 +34522,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="2">
@@ -34514,10 +34548,10 @@
         <v>794</v>
       </c>
       <c r="B2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D2" t="n">
         <v>5.56319513583543</v>
@@ -34537,10 +34571,10 @@
         <v>700</v>
       </c>
       <c r="B3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D3" t="n">
         <v>6.19142040473137</v>
@@ -34560,10 +34594,10 @@
         <v>700</v>
       </c>
       <c r="B4" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C4" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D4" t="n">
         <v>5.01499410140424</v>
@@ -34583,10 +34617,10 @@
         <v>700</v>
       </c>
       <c r="B5" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C5" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D5" t="n">
         <v>4.50042150457604</v>
@@ -34606,10 +34640,10 @@
         <v>700</v>
       </c>
       <c r="B6" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C6" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D6" t="n">
         <v>4.42285646470549</v>
@@ -34629,10 +34663,10 @@
         <v>700</v>
       </c>
       <c r="B7" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C7" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D7" t="n">
         <v>4.38163702315461</v>
@@ -34652,10 +34686,10 @@
         <v>795</v>
       </c>
       <c r="B8" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C8" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D8" t="n">
         <v>5.86866689634314</v>
@@ -34675,10 +34709,10 @@
         <v>795</v>
       </c>
       <c r="B9" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C9" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D9" t="n">
         <v>5.34056587767992</v>
@@ -34698,10 +34732,10 @@
         <v>713</v>
       </c>
       <c r="B10" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C10" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D10" t="n">
         <v>4.26558024436997</v>
@@ -34721,10 +34755,10 @@
         <v>796</v>
       </c>
       <c r="B11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C11" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D11" t="n">
         <v>4.2665699961584</v>
@@ -34744,10 +34778,10 @@
         <v>722</v>
       </c>
       <c r="B12" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C12" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D12" t="n">
         <v>4.30866207565557</v>
@@ -34767,10 +34801,10 @@
         <v>725</v>
       </c>
       <c r="B13" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C13" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D13" t="n">
         <v>5.91371493136742</v>
@@ -34790,10 +34824,10 @@
         <v>732</v>
       </c>
       <c r="B14" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C14" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D14" t="n">
         <v>7.94272577451758</v>
@@ -34813,10 +34847,10 @@
         <v>732</v>
       </c>
       <c r="B15" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C15" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D15" t="n">
         <v>6.13371443354996</v>
@@ -34836,10 +34870,10 @@
         <v>732</v>
       </c>
       <c r="B16" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C16" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D16" t="n">
         <v>5.20623335552779</v>
@@ -34859,10 +34893,10 @@
         <v>732</v>
       </c>
       <c r="B17" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C17" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D17" t="n">
         <v>4.65257825576127</v>
@@ -34882,10 +34916,10 @@
         <v>732</v>
       </c>
       <c r="B18" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C18" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D18" t="n">
         <v>4.49477402679512</v>
@@ -34905,10 +34939,10 @@
         <v>732</v>
       </c>
       <c r="B19" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C19" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D19" t="n">
         <v>4.31522912086201</v>
@@ -34928,10 +34962,10 @@
         <v>752</v>
       </c>
       <c r="B20" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C20" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D20" t="n">
         <v>4.18791593486781</v>
@@ -34951,10 +34985,10 @@
         <v>799</v>
       </c>
       <c r="B21" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C21" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D21" t="n">
         <v>6.2008269964468</v>
@@ -34974,10 +35008,10 @@
         <v>799</v>
       </c>
       <c r="B22" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C22" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D22" t="n">
         <v>5.41828352903867</v>
@@ -34997,10 +35031,10 @@
         <v>799</v>
       </c>
       <c r="B23" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C23" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D23" t="n">
         <v>5.18304253915878</v>
@@ -35020,10 +35054,10 @@
         <v>799</v>
       </c>
       <c r="B24" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C24" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D24" t="n">
         <v>5.12589755835554</v>
@@ -35043,10 +35077,10 @@
         <v>799</v>
       </c>
       <c r="B25" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C25" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D25" t="n">
         <v>4.8253762375682</v>
@@ -35066,10 +35100,10 @@
         <v>799</v>
       </c>
       <c r="B26" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C26" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="D26" t="n">
         <v>4.5890187383138</v>
@@ -35089,10 +35123,10 @@
         <v>799</v>
       </c>
       <c r="B27" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C27" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D27" t="n">
         <v>4.34900805535905</v>
@@ -35112,10 +35146,10 @@
         <v>799</v>
       </c>
       <c r="B28" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C28" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D28" t="n">
         <v>4.16077782806705</v>
@@ -35135,10 +35169,10 @@
         <v>800</v>
       </c>
       <c r="B29" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C29" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D29" t="n">
         <v>4.78212931113563</v>
@@ -35158,10 +35192,10 @@
         <v>800</v>
       </c>
       <c r="B30" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C30" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D30" t="n">
         <v>4.69634396374594</v>
@@ -35181,10 +35215,10 @@
         <v>801</v>
       </c>
       <c r="B31" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C31" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D31" t="n">
         <v>5.15222936251189</v>
@@ -35204,10 +35238,10 @@
         <v>801</v>
       </c>
       <c r="B32" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C32" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D32" t="n">
         <v>4.55398660085567</v>
@@ -35227,10 +35261,10 @@
         <v>801</v>
       </c>
       <c r="B33" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C33" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D33" t="n">
         <v>4.52711927543189</v>
@@ -35250,10 +35284,10 @@
         <v>801</v>
       </c>
       <c r="B34" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C34" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D34" t="n">
         <v>4.32619880184801</v>
@@ -35273,10 +35307,10 @@
         <v>772</v>
       </c>
       <c r="B35" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C35" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="D35" t="n">
         <v>5.21891345110117</v>
@@ -35296,10 +35330,10 @@
         <v>804</v>
       </c>
       <c r="B36" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C36" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D36" t="n">
         <v>4.80432723581206</v>
@@ -35319,10 +35353,10 @@
         <v>804</v>
       </c>
       <c r="B37" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C37" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D37" t="n">
         <v>4.74162375545968</v>
@@ -35342,10 +35376,10 @@
         <v>804</v>
       </c>
       <c r="B38" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C38" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="D38" t="n">
         <v>4.69445732512554</v>
@@ -35365,10 +35399,10 @@
         <v>805</v>
       </c>
       <c r="B39" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C39" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D39" t="n">
         <v>7.42012041205426</v>
@@ -35388,10 +35422,10 @@
         <v>805</v>
       </c>
       <c r="B40" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C40" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="D40" t="n">
         <v>5.63611173879047</v>
@@ -35411,10 +35445,10 @@
         <v>807</v>
       </c>
       <c r="B41" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C41" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D41" t="n">
         <v>5.87631165833241</v>
@@ -35456,57 +35490,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B2" t="s">
+        <v>979</v>
+      </c>
+      <c r="C2" t="s">
         <v>980</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>981</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>982</v>
-      </c>
-      <c r="D2" t="s">
-        <v>983</v>
-      </c>
-      <c r="E2" t="s">
-        <v>984</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -35524,27 +35558,27 @@
         <v>-10.8962</v>
       </c>
       <c r="K2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B3" t="s">
+        <v>985</v>
+      </c>
+      <c r="C3" t="s">
+        <v>986</v>
+      </c>
+      <c r="D3" t="s">
         <v>987</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>988</v>
-      </c>
-      <c r="D3" t="s">
-        <v>989</v>
-      </c>
-      <c r="E3" t="s">
-        <v>990</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -35562,27 +35596,27 @@
         <v>-10.8962</v>
       </c>
       <c r="K3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B4" t="s">
+        <v>990</v>
+      </c>
+      <c r="C4" t="s">
+        <v>991</v>
+      </c>
+      <c r="D4" t="s">
+        <v>987</v>
+      </c>
+      <c r="E4" t="s">
         <v>992</v>
-      </c>
-      <c r="C4" t="s">
-        <v>993</v>
-      </c>
-      <c r="D4" t="s">
-        <v>989</v>
-      </c>
-      <c r="E4" t="s">
-        <v>994</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -35600,27 +35634,27 @@
         <v>-9.24022</v>
       </c>
       <c r="K4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>994</v>
+      </c>
+      <c r="B5" t="s">
+        <v>995</v>
+      </c>
+      <c r="C5" t="s">
         <v>996</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>987</v>
+      </c>
+      <c r="E5" t="s">
         <v>997</v>
-      </c>
-      <c r="C5" t="s">
-        <v>998</v>
-      </c>
-      <c r="D5" t="s">
-        <v>989</v>
-      </c>
-      <c r="E5" t="s">
-        <v>999</v>
       </c>
       <c r="F5" t="n">
         <v>22</v>
@@ -35638,27 +35672,27 @@
         <v>18.4872</v>
       </c>
       <c r="K5" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>998</v>
+      </c>
+      <c r="B6" t="s">
+        <v>999</v>
+      </c>
+      <c r="C6" t="s">
         <v>1000</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>1001</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>1002</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1004</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
@@ -35676,27 +35710,27 @@
         <v>-28.3263</v>
       </c>
       <c r="K6" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L6" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
         <v>1005</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>1006</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>1007</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1009</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -35714,27 +35748,27 @@
         <v>-9.09692</v>
       </c>
       <c r="K7" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L7" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C8" t="s">
         <v>1010</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>1011</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>1012</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1014</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -35752,27 +35786,27 @@
         <v>-17.1398</v>
       </c>
       <c r="K8" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L8" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B9" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D9" t="s">
+        <v>987</v>
+      </c>
+      <c r="E9" t="s">
         <v>1015</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D9" t="s">
-        <v>989</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1017</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -35790,27 +35824,27 @@
         <v>-17.1398</v>
       </c>
       <c r="K9" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L9" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B10" t="s">
+        <v>889</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D10" t="s">
+        <v>987</v>
+      </c>
+      <c r="E10" t="s">
         <v>1018</v>
-      </c>
-      <c r="B10" t="s">
-        <v>891</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D10" t="s">
-        <v>989</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1020</v>
       </c>
       <c r="F10"/>
       <c r="G10" t="n">
@@ -35826,27 +35860,27 @@
         <v>-54.6711</v>
       </c>
       <c r="K10" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L10" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D11" t="s">
+        <v>987</v>
+      </c>
+      <c r="E11" t="s">
         <v>1021</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D11" t="s">
-        <v>989</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1023</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
@@ -35864,27 +35898,27 @@
         <v>18.2657</v>
       </c>
       <c r="K11" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L11" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C12" t="s">
         <v>1024</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>987</v>
+      </c>
+      <c r="E12" t="s">
         <v>1025</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D12" t="s">
-        <v>989</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1027</v>
       </c>
       <c r="F12"/>
       <c r="G12" t="n">
@@ -35900,27 +35934,27 @@
         <v>-18.2134</v>
       </c>
       <c r="K12" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L12" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B13" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D13" t="s">
         <v>1028</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>1029</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1031</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -35938,27 +35972,27 @@
         <v>-28.4897</v>
       </c>
       <c r="K13" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L13" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B14" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D14" t="s">
         <v>1032</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>1033</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1035</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -35976,27 +36010,27 @@
         <v>-8.79083</v>
       </c>
       <c r="K14" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L14" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C15" t="s">
         <v>1036</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
+        <v>987</v>
+      </c>
+      <c r="E15" t="s">
         <v>1037</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D15" t="s">
-        <v>989</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1039</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
@@ -36014,27 +36048,27 @@
         <v>-7.80113</v>
       </c>
       <c r="K15" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L15" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B16" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D16" t="s">
+        <v>987</v>
+      </c>
+      <c r="E16" t="s">
         <v>1040</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D16" t="s">
-        <v>989</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1042</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -36052,27 +36086,27 @@
         <v>-8.54689</v>
       </c>
       <c r="K16" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L16" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B17" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D17" t="s">
         <v>1043</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>1044</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1046</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
@@ -36090,27 +36124,27 @@
         <v>-7.73883</v>
       </c>
       <c r="K17" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L17" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D18" t="s">
         <v>1047</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>1048</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1050</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -36128,27 +36162,27 @@
         <v>-8.44475</v>
       </c>
       <c r="K18" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L18" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D19" t="s">
         <v>1051</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>1052</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1054</v>
       </c>
       <c r="F19" t="n">
         <v>12</v>
@@ -36166,27 +36200,27 @@
         <v>-25.6501</v>
       </c>
       <c r="K19" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L19" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D20" t="s">
         <v>1055</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>1056</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1058</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -36204,27 +36238,27 @@
         <v>-18.0921</v>
       </c>
       <c r="K20" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L20" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B21" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D21" t="s">
         <v>1059</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>1060</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1062</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -36242,27 +36276,27 @@
         <v>-18.0921</v>
       </c>
       <c r="K21" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L21" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B22" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D22" t="s">
         <v>1063</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>1064</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1066</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -36280,27 +36314,27 @@
         <v>-18.0921</v>
       </c>
       <c r="K22" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L22" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B23" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D23" t="s">
         <v>1067</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>1068</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1070</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -36318,27 +36352,27 @@
         <v>-18.0921</v>
       </c>
       <c r="K23" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L23" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C24" t="s">
         <v>1071</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
+        <v>987</v>
+      </c>
+      <c r="E24" t="s">
         <v>1072</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D24" t="s">
-        <v>989</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1074</v>
       </c>
       <c r="F24"/>
       <c r="G24" t="n">
@@ -36354,27 +36388,27 @@
         <v>-35.5729</v>
       </c>
       <c r="K24" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L24" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B25" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D25" t="s">
         <v>1075</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>1076</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1078</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
@@ -36392,27 +36426,27 @@
         <v>-7.54418</v>
       </c>
       <c r="K25" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L25" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B26" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D26" t="s">
         <v>1079</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>1080</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1082</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
@@ -36430,27 +36464,27 @@
         <v>-7.54418</v>
       </c>
       <c r="K26" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L26" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D27" t="s">
+        <v>987</v>
+      </c>
+      <c r="E27" t="s">
         <v>1083</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D27" t="s">
-        <v>989</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1085</v>
       </c>
       <c r="F27" t="n">
         <v>9</v>
@@ -36468,27 +36502,27 @@
         <v>-7.54418</v>
       </c>
       <c r="K27" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L27" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C28" t="s">
         <v>1086</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>987</v>
+      </c>
+      <c r="E28" t="s">
         <v>1087</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D28" t="s">
-        <v>989</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1089</v>
       </c>
       <c r="F28" t="n">
         <v>2</v>
@@ -36506,27 +36540,27 @@
         <v>-38.3013</v>
       </c>
       <c r="K28" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L28" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B29" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D29" t="s">
         <v>1090</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
         <v>1091</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1093</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -36544,27 +36578,27 @@
         <v>-16.726</v>
       </c>
       <c r="K29" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L29" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C30" t="s">
         <v>1094</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
         <v>1095</v>
       </c>
-      <c r="C30" t="s">
+      <c r="E30" t="s">
         <v>1096</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1098</v>
       </c>
       <c r="F30" t="n">
         <v>21</v>
@@ -36582,27 +36616,27 @@
         <v>-11.8152</v>
       </c>
       <c r="K30" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L30" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B31" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D31" t="s">
+        <v>987</v>
+      </c>
+      <c r="E31" t="s">
         <v>1099</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>989</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1101</v>
       </c>
       <c r="F31" t="n">
         <v>21</v>
@@ -36620,27 +36654,27 @@
         <v>-11.8152</v>
       </c>
       <c r="K31" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L31" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B32" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D32" t="s">
         <v>1102</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>1103</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1104</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1105</v>
       </c>
       <c r="F32" t="n">
         <v>12</v>
@@ -36658,27 +36692,27 @@
         <v>-25.8367</v>
       </c>
       <c r="K32" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L32" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B33" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D33" t="s">
+        <v>987</v>
+      </c>
+      <c r="E33" t="s">
         <v>1106</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>989</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1108</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
@@ -36696,27 +36730,27 @@
         <v>-37.8698</v>
       </c>
       <c r="K33" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L33" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C34" t="s">
         <v>1109</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D34" t="s">
         <v>1110</v>
       </c>
-      <c r="C34" t="s">
+      <c r="E34" t="s">
         <v>1111</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1113</v>
       </c>
       <c r="F34"/>
       <c r="G34" t="n">
@@ -36732,27 +36766,27 @@
         <v>9.21609</v>
       </c>
       <c r="K34" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L34" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B35" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D35" t="s">
+        <v>987</v>
+      </c>
+      <c r="E35" t="s">
         <v>1114</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D35" t="s">
-        <v>989</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1116</v>
       </c>
       <c r="F35"/>
       <c r="G35" t="n">
@@ -36768,27 +36802,27 @@
         <v>9.21609</v>
       </c>
       <c r="K35" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L35" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B36" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D36" t="s">
         <v>1117</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E36" t="s">
         <v>1118</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1120</v>
       </c>
       <c r="F36" t="n">
         <v>9</v>
@@ -36806,27 +36840,27 @@
         <v>-7.34136</v>
       </c>
       <c r="K36" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L36" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B37" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D37" t="s">
         <v>1121</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E37" t="s">
         <v>1122</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1124</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
@@ -36844,27 +36878,27 @@
         <v>-7.34136</v>
       </c>
       <c r="K37" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L37" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B38" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D38" t="s">
+        <v>987</v>
+      </c>
+      <c r="E38" t="s">
         <v>1125</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D38" t="s">
-        <v>989</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1127</v>
       </c>
       <c r="F38" t="n">
         <v>9</v>
@@ -36882,27 +36916,27 @@
         <v>-7.34136</v>
       </c>
       <c r="K38" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L38" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B39" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D39" t="s">
+        <v>987</v>
+      </c>
+      <c r="E39" t="s">
         <v>1128</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D39" t="s">
-        <v>989</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1130</v>
       </c>
       <c r="F39" t="n">
         <v>9</v>
@@ -36920,27 +36954,27 @@
         <v>-7.34136</v>
       </c>
       <c r="K39" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L39" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B40" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D40" t="s">
         <v>1131</v>
       </c>
-      <c r="C40" t="s">
+      <c r="E40" t="s">
         <v>1132</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1134</v>
       </c>
       <c r="F40" t="n">
         <v>9</v>
@@ -36958,27 +36992,27 @@
         <v>-7.34136</v>
       </c>
       <c r="K40" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L40" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B41" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D41" t="s">
         <v>1135</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>1136</v>
-      </c>
-      <c r="D41" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1138</v>
       </c>
       <c r="F41" t="n">
         <v>9</v>
@@ -36996,27 +37030,27 @@
         <v>-7.34136</v>
       </c>
       <c r="K41" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L41" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B42" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D42" t="s">
+        <v>987</v>
+      </c>
+      <c r="E42" t="s">
         <v>1139</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D42" t="s">
-        <v>989</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1141</v>
       </c>
       <c r="F42" t="n">
         <v>9</v>
@@ -37034,27 +37068,27 @@
         <v>-7.23409</v>
       </c>
       <c r="K42" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L42" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B43" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D43" t="s">
         <v>1142</v>
       </c>
-      <c r="C43" t="s">
+      <c r="E43" t="s">
         <v>1143</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1144</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1145</v>
       </c>
       <c r="F43" t="n">
         <v>9</v>
@@ -37072,27 +37106,27 @@
         <v>-7.23409</v>
       </c>
       <c r="K43" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L43" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B44" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D44" t="s">
         <v>1146</v>
       </c>
-      <c r="C44" t="s">
+      <c r="E44" t="s">
         <v>1147</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1149</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -37110,27 +37144,27 @@
         <v>-16.025</v>
       </c>
       <c r="K44" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L44" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C45" t="s">
         <v>1150</v>
       </c>
-      <c r="B45" t="s">
+      <c r="D45" t="s">
         <v>1151</v>
       </c>
-      <c r="C45" t="s">
+      <c r="E45" t="s">
         <v>1152</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1154</v>
       </c>
       <c r="F45"/>
       <c r="G45" t="n">
@@ -37146,27 +37180,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K45" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L45" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B46" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D46" t="s">
         <v>1155</v>
       </c>
-      <c r="C46" t="s">
+      <c r="E46" t="s">
         <v>1156</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1158</v>
       </c>
       <c r="F46"/>
       <c r="G46" t="n">
@@ -37182,27 +37216,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K46" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L46" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B47" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D47" t="s">
         <v>1159</v>
       </c>
-      <c r="C47" t="s">
+      <c r="E47" t="s">
         <v>1160</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1162</v>
       </c>
       <c r="F47"/>
       <c r="G47" t="n">
@@ -37218,27 +37252,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K47" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L47" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B48" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D48" t="s">
+        <v>987</v>
+      </c>
+      <c r="E48" t="s">
         <v>1163</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D48" t="s">
-        <v>989</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1165</v>
       </c>
       <c r="F48"/>
       <c r="G48" t="n">
@@ -37254,27 +37288,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K48" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L48" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B49" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D49" t="s">
         <v>1166</v>
       </c>
-      <c r="C49" t="s">
+      <c r="E49" t="s">
         <v>1167</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1168</v>
-      </c>
-      <c r="E49" t="s">
-        <v>1169</v>
       </c>
       <c r="F49"/>
       <c r="G49" t="n">
@@ -37290,27 +37324,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K49" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L49" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B50" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D50" t="s">
         <v>1170</v>
       </c>
-      <c r="C50" t="s">
+      <c r="E50" t="s">
         <v>1171</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1173</v>
       </c>
       <c r="F50"/>
       <c r="G50" t="n">
@@ -37326,27 +37360,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K50" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L50" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B51" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D51" t="s">
         <v>1174</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>1175</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1176</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1177</v>
       </c>
       <c r="F51"/>
       <c r="G51" t="n">
@@ -37362,27 +37396,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K51" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L51" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B52" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D52" t="s">
         <v>1178</v>
       </c>
-      <c r="C52" t="s">
+      <c r="E52" t="s">
         <v>1179</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1180</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1181</v>
       </c>
       <c r="F52"/>
       <c r="G52" t="n">
@@ -37398,27 +37432,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K52" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L52" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B53" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D53" t="s">
+        <v>987</v>
+      </c>
+      <c r="E53" t="s">
         <v>1182</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D53" t="s">
-        <v>989</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1184</v>
       </c>
       <c r="F53"/>
       <c r="G53" t="n">
@@ -37434,27 +37468,27 @@
         <v>-8.66055</v>
       </c>
       <c r="K53" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L53" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B54" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D54" t="s">
         <v>1185</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E54" t="s">
         <v>1186</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E54" t="s">
-        <v>1188</v>
       </c>
       <c r="F54" t="n">
         <v>9</v>
@@ -37472,27 +37506,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K54" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L54" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B55" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D55" t="s">
         <v>1189</v>
       </c>
-      <c r="C55" t="s">
+      <c r="E55" t="s">
         <v>1190</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1192</v>
       </c>
       <c r="F55" t="n">
         <v>9</v>
@@ -37510,27 +37544,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K55" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L55" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B56" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D56" t="s">
         <v>1193</v>
       </c>
-      <c r="C56" t="s">
+      <c r="E56" t="s">
         <v>1194</v>
-      </c>
-      <c r="D56" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E56" t="s">
-        <v>1196</v>
       </c>
       <c r="F56" t="n">
         <v>9</v>
@@ -37548,27 +37582,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K56" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L56" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B57" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D57" t="s">
         <v>1197</v>
       </c>
-      <c r="C57" t="s">
+      <c r="E57" t="s">
         <v>1198</v>
-      </c>
-      <c r="D57" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E57" t="s">
-        <v>1200</v>
       </c>
       <c r="F57" t="n">
         <v>9</v>
@@ -37586,27 +37620,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K57" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L57" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B58" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D58" t="s">
         <v>1201</v>
       </c>
-      <c r="C58" t="s">
+      <c r="E58" t="s">
         <v>1202</v>
-      </c>
-      <c r="D58" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E58" t="s">
-        <v>1204</v>
       </c>
       <c r="F58" t="n">
         <v>9</v>
@@ -37624,27 +37658,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K58" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L58" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B59" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D59" t="s">
         <v>1205</v>
       </c>
-      <c r="C59" t="s">
+      <c r="E59" t="s">
         <v>1206</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1208</v>
       </c>
       <c r="F59" t="n">
         <v>9</v>
@@ -37662,27 +37696,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K59" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L59" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B60" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D60" t="s">
         <v>1209</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>1210</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1211</v>
-      </c>
-      <c r="E60" t="s">
-        <v>1212</v>
       </c>
       <c r="F60" t="n">
         <v>9</v>
@@ -37700,27 +37734,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K60" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L60" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B61" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D61" t="s">
         <v>1213</v>
       </c>
-      <c r="C61" t="s">
+      <c r="E61" t="s">
         <v>1214</v>
-      </c>
-      <c r="D61" t="s">
-        <v>1215</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1216</v>
       </c>
       <c r="F61" t="n">
         <v>9</v>
@@ -37738,27 +37772,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K61" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L61" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B62" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D62" t="s">
+        <v>987</v>
+      </c>
+      <c r="E62" t="s">
         <v>1217</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D62" t="s">
-        <v>989</v>
-      </c>
-      <c r="E62" t="s">
-        <v>1219</v>
       </c>
       <c r="F62" t="n">
         <v>9</v>
@@ -37776,27 +37810,27 @@
         <v>-7.10739</v>
       </c>
       <c r="K62" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L62" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B63" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D63" t="s">
+        <v>987</v>
+      </c>
+      <c r="E63" t="s">
         <v>1220</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D63" t="s">
-        <v>989</v>
-      </c>
-      <c r="E63" t="s">
-        <v>1222</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
@@ -37814,27 +37848,27 @@
         <v>-35.6024</v>
       </c>
       <c r="K63" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L63" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B64" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D64" t="s">
         <v>1223</v>
       </c>
-      <c r="C64" t="s">
+      <c r="E64" t="s">
         <v>1224</v>
-      </c>
-      <c r="D64" t="s">
-        <v>1225</v>
-      </c>
-      <c r="E64" t="s">
-        <v>1226</v>
       </c>
       <c r="F64" t="n">
         <v>9</v>
@@ -37852,27 +37886,27 @@
         <v>-7.08925</v>
       </c>
       <c r="K64" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L64" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B65" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D65" t="s">
+        <v>987</v>
+      </c>
+      <c r="E65" t="s">
         <v>1227</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D65" t="s">
-        <v>989</v>
-      </c>
-      <c r="E65" t="s">
-        <v>1229</v>
       </c>
       <c r="F65" t="n">
         <v>5</v>
@@ -37890,27 +37924,27 @@
         <v>-14.8402</v>
       </c>
       <c r="K65" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L65" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C66" t="s">
         <v>1230</v>
       </c>
-      <c r="B66" t="s">
+      <c r="D66" t="s">
+        <v>987</v>
+      </c>
+      <c r="E66" t="s">
         <v>1231</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1232</v>
-      </c>
-      <c r="D66" t="s">
-        <v>989</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1233</v>
       </c>
       <c r="F66" t="n">
         <v>7</v>
@@ -37928,27 +37962,27 @@
         <v>-16.3852</v>
       </c>
       <c r="K66" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L66" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B67" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D67" t="s">
         <v>1234</v>
       </c>
-      <c r="C67" t="s">
+      <c r="E67" t="s">
         <v>1235</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1237</v>
       </c>
       <c r="F67" t="n">
         <v>7</v>
@@ -37966,27 +38000,27 @@
         <v>-16.3852</v>
       </c>
       <c r="K67" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L67" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C68" t="s">
         <v>1238</v>
       </c>
-      <c r="B68" t="s">
+      <c r="D68" t="s">
+        <v>987</v>
+      </c>
+      <c r="E68" t="s">
         <v>1239</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D68" t="s">
-        <v>989</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1241</v>
       </c>
       <c r="F68" t="n">
         <v>20</v>
@@ -38004,27 +38038,27 @@
         <v>-7.28691</v>
       </c>
       <c r="K68" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L68" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B69" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D69" t="s">
         <v>1242</v>
       </c>
-      <c r="C69" t="s">
+      <c r="E69" t="s">
         <v>1243</v>
-      </c>
-      <c r="D69" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1245</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -38042,27 +38076,27 @@
         <v>-35.075</v>
       </c>
       <c r="K69" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L69" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B70" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D70" t="s">
         <v>1246</v>
       </c>
-      <c r="C70" t="s">
+      <c r="E70" t="s">
         <v>1247</v>
-      </c>
-      <c r="D70" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E70" t="s">
-        <v>1249</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -38080,27 +38114,27 @@
         <v>-35.075</v>
       </c>
       <c r="K70" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L70" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B71" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D71" t="s">
         <v>1250</v>
       </c>
-      <c r="C71" t="s">
+      <c r="E71" t="s">
         <v>1251</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E71" t="s">
-        <v>1253</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -38118,27 +38152,27 @@
         <v>-35.075</v>
       </c>
       <c r="K71" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L71" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B72" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D72" t="s">
         <v>1254</v>
       </c>
-      <c r="C72" t="s">
+      <c r="E72" t="s">
         <v>1255</v>
-      </c>
-      <c r="D72" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E72" t="s">
-        <v>1257</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -38156,27 +38190,27 @@
         <v>-35.075</v>
       </c>
       <c r="K72" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L72" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B73" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D73" t="s">
         <v>1258</v>
       </c>
-      <c r="C73" t="s">
+      <c r="E73" t="s">
         <v>1259</v>
-      </c>
-      <c r="D73" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E73" t="s">
-        <v>1261</v>
       </c>
       <c r="F73" t="n">
         <v>9</v>
@@ -38194,27 +38228,27 @@
         <v>-6.69938</v>
       </c>
       <c r="K73" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L73" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B74" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D74" t="s">
+        <v>987</v>
+      </c>
+      <c r="E74" t="s">
         <v>1262</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D74" t="s">
-        <v>989</v>
-      </c>
-      <c r="E74" t="s">
-        <v>1264</v>
       </c>
       <c r="F74" t="n">
         <v>9</v>
@@ -38232,27 +38266,27 @@
         <v>-6.69938</v>
       </c>
       <c r="K74" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L74" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B75" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D75" t="s">
+        <v>987</v>
+      </c>
+      <c r="E75" t="s">
         <v>1265</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D75" t="s">
-        <v>989</v>
-      </c>
-      <c r="E75" t="s">
-        <v>1267</v>
       </c>
       <c r="F75" t="n">
         <v>9</v>
@@ -38270,27 +38304,27 @@
         <v>-6.69283</v>
       </c>
       <c r="K75" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L75" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B76" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D76" t="s">
         <v>1268</v>
       </c>
-      <c r="C76" t="s">
+      <c r="E76" t="s">
         <v>1269</v>
-      </c>
-      <c r="D76" t="s">
-        <v>1270</v>
-      </c>
-      <c r="E76" t="s">
-        <v>1271</v>
       </c>
       <c r="F76" t="n">
         <v>5</v>
@@ -38308,27 +38342,27 @@
         <v>-14.3903</v>
       </c>
       <c r="K76" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L76" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B77" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D77" t="s">
         <v>1272</v>
       </c>
-      <c r="C77" t="s">
+      <c r="E77" t="s">
         <v>1273</v>
-      </c>
-      <c r="D77" t="s">
-        <v>1274</v>
-      </c>
-      <c r="E77" t="s">
-        <v>1275</v>
       </c>
       <c r="F77"/>
       <c r="G77" t="n">
@@ -38344,27 +38378,27 @@
         <v>-30.8523</v>
       </c>
       <c r="K77" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L77" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B78" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D78" t="s">
         <v>1276</v>
       </c>
-      <c r="C78" t="s">
+      <c r="E78" t="s">
         <v>1277</v>
-      </c>
-      <c r="D78" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1279</v>
       </c>
       <c r="F78"/>
       <c r="G78" t="n">
@@ -38380,27 +38414,27 @@
         <v>-30.8523</v>
       </c>
       <c r="K78" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L78" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B79" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D79" t="s">
+        <v>987</v>
+      </c>
+      <c r="E79" t="s">
         <v>1280</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D79" t="s">
-        <v>989</v>
-      </c>
-      <c r="E79" t="s">
-        <v>1282</v>
       </c>
       <c r="F79"/>
       <c r="G79" t="n">
@@ -38416,27 +38450,27 @@
         <v>-30.8523</v>
       </c>
       <c r="K79" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L79" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B80" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E80" t="s">
         <v>1283</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1284</v>
-      </c>
-      <c r="D80" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E80" t="s">
-        <v>1285</v>
       </c>
       <c r="F80"/>
       <c r="G80" t="n">
@@ -38452,27 +38486,27 @@
         <v>-30.8523</v>
       </c>
       <c r="K80" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L80" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B81" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E81" t="s">
         <v>1286</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D81" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E81" t="s">
-        <v>1288</v>
       </c>
       <c r="F81"/>
       <c r="G81" t="n">
@@ -38488,27 +38522,27 @@
         <v>-30.8523</v>
       </c>
       <c r="K81" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L81" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B82" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E82" t="s">
         <v>1289</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D82" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E82" t="s">
-        <v>1291</v>
       </c>
       <c r="F82"/>
       <c r="G82" t="n">
@@ -38524,27 +38558,27 @@
         <v>-30.8523</v>
       </c>
       <c r="K82" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L82" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B83" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D83" t="s">
         <v>1292</v>
       </c>
-      <c r="C83" t="s">
+      <c r="E83" t="s">
         <v>1293</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1294</v>
-      </c>
-      <c r="E83" t="s">
-        <v>1295</v>
       </c>
       <c r="F83" t="n">
         <v>9</v>
@@ -38562,27 +38596,27 @@
         <v>-6.52098</v>
       </c>
       <c r="K83" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L83" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B84" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D84" t="s">
         <v>1296</v>
       </c>
-      <c r="C84" t="s">
+      <c r="E84" t="s">
         <v>1297</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1298</v>
-      </c>
-      <c r="E84" t="s">
-        <v>1299</v>
       </c>
       <c r="F84" t="n">
         <v>9</v>
@@ -38600,27 +38634,27 @@
         <v>-6.52098</v>
       </c>
       <c r="K84" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L84" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B85" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D85" t="s">
         <v>1300</v>
       </c>
-      <c r="C85" t="s">
+      <c r="E85" t="s">
         <v>1301</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1302</v>
-      </c>
-      <c r="E85" t="s">
-        <v>1303</v>
       </c>
       <c r="F85" t="n">
         <v>9</v>
@@ -38638,27 +38672,27 @@
         <v>-6.52098</v>
       </c>
       <c r="K85" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L85" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B86" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D86" t="s">
         <v>1304</v>
       </c>
-      <c r="C86" t="s">
+      <c r="E86" t="s">
         <v>1305</v>
-      </c>
-      <c r="D86" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E86" t="s">
-        <v>1307</v>
       </c>
       <c r="F86" t="n">
         <v>9</v>
@@ -38676,27 +38710,27 @@
         <v>-6.495</v>
       </c>
       <c r="K86" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L86" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B87" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D87" t="s">
         <v>1308</v>
       </c>
-      <c r="C87" t="s">
+      <c r="E87" t="s">
         <v>1309</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1310</v>
-      </c>
-      <c r="E87" t="s">
-        <v>1311</v>
       </c>
       <c r="F87" t="n">
         <v>9</v>
@@ -38714,27 +38748,27 @@
         <v>-6.49457</v>
       </c>
       <c r="K87" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L87" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B88" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D88" t="s">
         <v>1312</v>
       </c>
-      <c r="C88" t="s">
+      <c r="E88" t="s">
         <v>1313</v>
-      </c>
-      <c r="D88" t="s">
-        <v>1314</v>
-      </c>
-      <c r="E88" t="s">
-        <v>1315</v>
       </c>
       <c r="F88" t="n">
         <v>7</v>
@@ -38752,27 +38786,27 @@
         <v>-14.8966</v>
       </c>
       <c r="K88" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L88" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B89" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D89" t="s">
+        <v>987</v>
+      </c>
+      <c r="E89" t="s">
         <v>1316</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1317</v>
-      </c>
-      <c r="D89" t="s">
-        <v>989</v>
-      </c>
-      <c r="E89" t="s">
-        <v>1318</v>
       </c>
       <c r="F89" t="n">
         <v>7</v>
@@ -38790,27 +38824,27 @@
         <v>-14.8966</v>
       </c>
       <c r="K89" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L89" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B90" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D90" t="s">
         <v>1319</v>
       </c>
-      <c r="C90" t="s">
+      <c r="E90" t="s">
         <v>1320</v>
-      </c>
-      <c r="D90" t="s">
-        <v>1321</v>
-      </c>
-      <c r="E90" t="s">
-        <v>1322</v>
       </c>
       <c r="F90" t="n">
         <v>9</v>
@@ -38828,27 +38862,27 @@
         <v>-6.71463</v>
       </c>
       <c r="K90" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L90" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B91" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E91" t="s">
         <v>1323</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D91" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E91" t="s">
-        <v>1325</v>
       </c>
       <c r="F91" t="n">
         <v>9</v>
@@ -38866,27 +38900,27 @@
         <v>-6.71463</v>
       </c>
       <c r="K91" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L91" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B92" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D92" t="s">
         <v>1326</v>
       </c>
-      <c r="C92" t="s">
+      <c r="E92" t="s">
         <v>1327</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1328</v>
-      </c>
-      <c r="E92" t="s">
-        <v>1329</v>
       </c>
       <c r="F92" t="n">
         <v>7</v>
@@ -38904,27 +38938,27 @@
         <v>-14.2354</v>
       </c>
       <c r="K92" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L92" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C93" t="s">
         <v>1330</v>
       </c>
-      <c r="B93" t="s">
+      <c r="D93" t="s">
         <v>1331</v>
       </c>
-      <c r="C93" t="s">
+      <c r="E93" t="s">
         <v>1332</v>
-      </c>
-      <c r="D93" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E93" t="s">
-        <v>1334</v>
       </c>
       <c r="F93" t="n">
         <v>16</v>
@@ -38942,27 +38976,27 @@
         <v>15.7558</v>
       </c>
       <c r="K93" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L93" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C94" t="s">
         <v>1335</v>
       </c>
-      <c r="B94" t="s">
+      <c r="D94" t="s">
         <v>1336</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94" t="s">
         <v>1337</v>
-      </c>
-      <c r="D94" t="s">
-        <v>1338</v>
-      </c>
-      <c r="E94" t="s">
-        <v>1339</v>
       </c>
       <c r="F94"/>
       <c r="G94" t="n">
@@ -38978,27 +39012,27 @@
         <v>26.185</v>
       </c>
       <c r="K94" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L94" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B95" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D95" t="s">
+        <v>987</v>
+      </c>
+      <c r="E95" t="s">
         <v>1340</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D95" t="s">
-        <v>989</v>
-      </c>
-      <c r="E95" t="s">
-        <v>1342</v>
       </c>
       <c r="F95" t="n">
         <v>21</v>
@@ -39016,27 +39050,27 @@
         <v>-10.2004</v>
       </c>
       <c r="K95" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L95" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C96" t="s">
         <v>1343</v>
       </c>
-      <c r="B96" t="s">
+      <c r="D96" t="s">
         <v>1344</v>
       </c>
-      <c r="C96" t="s">
+      <c r="E96" t="s">
         <v>1345</v>
-      </c>
-      <c r="D96" t="s">
-        <v>1346</v>
-      </c>
-      <c r="E96" t="s">
-        <v>1347</v>
       </c>
       <c r="F96"/>
       <c r="G96" t="n">
@@ -39052,27 +39086,27 @@
         <v>10.9106</v>
       </c>
       <c r="K96" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L96" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B97" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D97" t="s">
         <v>1348</v>
       </c>
-      <c r="C97" t="s">
+      <c r="E97" t="s">
         <v>1349</v>
-      </c>
-      <c r="D97" t="s">
-        <v>1350</v>
-      </c>
-      <c r="E97" t="s">
-        <v>1351</v>
       </c>
       <c r="F97"/>
       <c r="G97" t="n">
@@ -39088,27 +39122,27 @@
         <v>10.9106</v>
       </c>
       <c r="K97" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L97" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B98" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D98" t="s">
+        <v>987</v>
+      </c>
+      <c r="E98" t="s">
         <v>1352</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1353</v>
-      </c>
-      <c r="D98" t="s">
-        <v>989</v>
-      </c>
-      <c r="E98" t="s">
-        <v>1354</v>
       </c>
       <c r="F98"/>
       <c r="G98" t="n">
@@ -39124,27 +39158,27 @@
         <v>10.9106</v>
       </c>
       <c r="K98" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L98" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B99" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D99" t="s">
         <v>1355</v>
       </c>
-      <c r="C99" t="s">
+      <c r="E99" t="s">
         <v>1356</v>
-      </c>
-      <c r="D99" t="s">
-        <v>1357</v>
-      </c>
-      <c r="E99" t="s">
-        <v>1358</v>
       </c>
       <c r="F99"/>
       <c r="G99" t="n">
@@ -39160,27 +39194,27 @@
         <v>8.3463</v>
       </c>
       <c r="K99" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L99" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B100" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D100" t="s">
+        <v>987</v>
+      </c>
+      <c r="E100" t="s">
         <v>1359</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1360</v>
-      </c>
-      <c r="D100" t="s">
-        <v>989</v>
-      </c>
-      <c r="E100" t="s">
-        <v>1361</v>
       </c>
       <c r="F100"/>
       <c r="G100" t="n">
@@ -39196,27 +39230,27 @@
         <v>8.3463</v>
       </c>
       <c r="K100" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L100" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B101" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D101" t="s">
         <v>1362</v>
       </c>
-      <c r="C101" t="s">
+      <c r="E101" t="s">
         <v>1363</v>
-      </c>
-      <c r="D101" t="s">
-        <v>1364</v>
-      </c>
-      <c r="E101" t="s">
-        <v>1365</v>
       </c>
       <c r="F101"/>
       <c r="G101" t="n">
@@ -39232,27 +39266,27 @@
         <v>8.3463</v>
       </c>
       <c r="K101" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L101" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B102" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D102" t="s">
+        <v>987</v>
+      </c>
+      <c r="E102" t="s">
         <v>1366</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D102" t="s">
-        <v>989</v>
-      </c>
-      <c r="E102" t="s">
-        <v>1368</v>
       </c>
       <c r="F102"/>
       <c r="G102" t="n">
@@ -39268,27 +39302,27 @@
         <v>8.3463</v>
       </c>
       <c r="K102" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L102" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B103" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E103" t="s">
         <v>1369</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D103" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E103" t="s">
-        <v>1371</v>
       </c>
       <c r="F103"/>
       <c r="G103" t="n">
@@ -39304,27 +39338,27 @@
         <v>8.3463</v>
       </c>
       <c r="K103" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L103" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C104" t="s">
         <v>1372</v>
       </c>
-      <c r="B104" t="s">
+      <c r="D104" t="s">
         <v>1373</v>
       </c>
-      <c r="C104" t="s">
+      <c r="E104" t="s">
         <v>1374</v>
-      </c>
-      <c r="D104" t="s">
-        <v>1375</v>
-      </c>
-      <c r="E104" t="s">
-        <v>1376</v>
       </c>
       <c r="F104" t="n">
         <v>4</v>
@@ -39342,27 +39376,27 @@
         <v>12.0098</v>
       </c>
       <c r="K104" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L104" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B105" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D105" t="s">
         <v>1377</v>
       </c>
-      <c r="C105" t="s">
+      <c r="E105" t="s">
         <v>1378</v>
-      </c>
-      <c r="D105" t="s">
-        <v>1379</v>
-      </c>
-      <c r="E105" t="s">
-        <v>1380</v>
       </c>
       <c r="F105" t="n">
         <v>22</v>
@@ -39380,27 +39414,27 @@
         <v>14.6223</v>
       </c>
       <c r="K105" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L105" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C106" t="s">
         <v>1381</v>
       </c>
-      <c r="B106" t="s">
+      <c r="D106" t="s">
         <v>1382</v>
       </c>
-      <c r="C106" t="s">
+      <c r="E106" t="s">
         <v>1383</v>
-      </c>
-      <c r="D106" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E106" t="s">
-        <v>1385</v>
       </c>
       <c r="F106" t="n">
         <v>17</v>
@@ -39418,27 +39452,27 @@
         <v>21.585</v>
       </c>
       <c r="K106" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L106" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B107" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D107" t="s">
+        <v>987</v>
+      </c>
+      <c r="E107" t="s">
         <v>1386</v>
-      </c>
-      <c r="C107" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D107" t="s">
-        <v>989</v>
-      </c>
-      <c r="E107" t="s">
-        <v>1388</v>
       </c>
       <c r="F107" t="n">
         <v>17</v>
@@ -39456,27 +39490,27 @@
         <v>21.9015</v>
       </c>
       <c r="K107" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L107" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C108" t="s">
         <v>1389</v>
       </c>
-      <c r="B108" t="s">
+      <c r="D108" t="s">
         <v>1390</v>
       </c>
-      <c r="C108" t="s">
+      <c r="E108" t="s">
         <v>1391</v>
-      </c>
-      <c r="D108" t="s">
-        <v>1392</v>
-      </c>
-      <c r="E108" t="s">
-        <v>1393</v>
       </c>
       <c r="F108"/>
       <c r="G108" t="n">
@@ -39492,27 +39526,27 @@
         <v>17.4978</v>
       </c>
       <c r="K108" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L108" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C109" t="s">
         <v>1394</v>
       </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
         <v>1395</v>
       </c>
-      <c r="C109" t="s">
+      <c r="E109" t="s">
         <v>1396</v>
-      </c>
-      <c r="D109" t="s">
-        <v>1397</v>
-      </c>
-      <c r="E109" t="s">
-        <v>1398</v>
       </c>
       <c r="F109"/>
       <c r="G109" t="n">
@@ -39528,27 +39562,27 @@
         <v>16.5498</v>
       </c>
       <c r="K109" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L109" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C110" t="s">
         <v>1399</v>
       </c>
-      <c r="B110" t="s">
+      <c r="D110" t="s">
         <v>1400</v>
       </c>
-      <c r="C110" t="s">
+      <c r="E110" t="s">
         <v>1401</v>
-      </c>
-      <c r="D110" t="s">
-        <v>1402</v>
-      </c>
-      <c r="E110" t="s">
-        <v>1403</v>
       </c>
       <c r="F110" t="n">
         <v>19</v>
@@ -39566,27 +39600,27 @@
         <v>-20.9067</v>
       </c>
       <c r="K110" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L110" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C111" t="s">
         <v>1404</v>
       </c>
-      <c r="B111" t="s">
+      <c r="D111" t="s">
+        <v>987</v>
+      </c>
+      <c r="E111" t="s">
         <v>1405</v>
-      </c>
-      <c r="C111" t="s">
-        <v>1406</v>
-      </c>
-      <c r="D111" t="s">
-        <v>989</v>
-      </c>
-      <c r="E111" t="s">
-        <v>1407</v>
       </c>
       <c r="F111" t="n">
         <v>18</v>
@@ -39604,27 +39638,27 @@
         <v>-6.68635</v>
       </c>
       <c r="K111" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L111" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B112" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D112" t="s">
+        <v>987</v>
+      </c>
+      <c r="E112" t="s">
         <v>1408</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D112" t="s">
-        <v>989</v>
-      </c>
-      <c r="E112" t="s">
-        <v>1410</v>
       </c>
       <c r="F112" t="n">
         <v>18</v>
@@ -39642,27 +39676,27 @@
         <v>-6.81021</v>
       </c>
       <c r="K112" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L112" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B113" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D113" t="s">
+        <v>987</v>
+      </c>
+      <c r="E113" t="s">
         <v>1411</v>
-      </c>
-      <c r="C113" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D113" t="s">
-        <v>989</v>
-      </c>
-      <c r="E113" t="s">
-        <v>1413</v>
       </c>
       <c r="F113" t="n">
         <v>18</v>
@@ -39680,27 +39714,27 @@
         <v>-6.6629</v>
       </c>
       <c r="K113" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L113" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C114" t="s">
         <v>1414</v>
       </c>
-      <c r="B114" t="s">
+      <c r="D114" t="s">
         <v>1415</v>
       </c>
-      <c r="C114" t="s">
+      <c r="E114" t="s">
         <v>1416</v>
-      </c>
-      <c r="D114" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E114" t="s">
-        <v>1418</v>
       </c>
       <c r="F114"/>
       <c r="G114" t="n">
@@ -39716,27 +39750,27 @@
         <v>-12.7805</v>
       </c>
       <c r="K114" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L114" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B115" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D115" t="s">
+        <v>987</v>
+      </c>
+      <c r="E115" t="s">
         <v>1419</v>
-      </c>
-      <c r="C115" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D115" t="s">
-        <v>989</v>
-      </c>
-      <c r="E115" t="s">
-        <v>1421</v>
       </c>
       <c r="F115"/>
       <c r="G115" t="n">
@@ -39752,27 +39786,27 @@
         <v>-12.7805</v>
       </c>
       <c r="K115" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L115" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B116" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D116" t="s">
+        <v>987</v>
+      </c>
+      <c r="E116" t="s">
         <v>1422</v>
-      </c>
-      <c r="C116" t="s">
-        <v>1423</v>
-      </c>
-      <c r="D116" t="s">
-        <v>989</v>
-      </c>
-      <c r="E116" t="s">
-        <v>1424</v>
       </c>
       <c r="F116"/>
       <c r="G116" t="n">
@@ -39788,27 +39822,27 @@
         <v>-12.7805</v>
       </c>
       <c r="K116" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L116" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B117" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D117" t="s">
         <v>1425</v>
       </c>
-      <c r="C117" t="s">
+      <c r="E117" t="s">
         <v>1426</v>
-      </c>
-      <c r="D117" t="s">
-        <v>1427</v>
-      </c>
-      <c r="E117" t="s">
-        <v>1428</v>
       </c>
       <c r="F117"/>
       <c r="G117" t="n">
@@ -39824,27 +39858,27 @@
         <v>20.0848</v>
       </c>
       <c r="K117" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L117" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B118" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D118" t="s">
         <v>1429</v>
       </c>
-      <c r="C118" t="s">
+      <c r="E118" t="s">
         <v>1430</v>
-      </c>
-      <c r="D118" t="s">
-        <v>1431</v>
-      </c>
-      <c r="E118" t="s">
-        <v>1432</v>
       </c>
       <c r="F118"/>
       <c r="G118" t="n">
@@ -39860,27 +39894,27 @@
         <v>20.0848</v>
       </c>
       <c r="K118" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L118" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C119" t="s">
         <v>1433</v>
       </c>
-      <c r="B119" t="s">
+      <c r="D119" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E119" t="s">
         <v>1434</v>
-      </c>
-      <c r="C119" t="s">
-        <v>1435</v>
-      </c>
-      <c r="D119" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E119" t="s">
-        <v>1436</v>
       </c>
       <c r="F119" t="n">
         <v>6</v>
@@ -39898,27 +39932,27 @@
         <v>-31.4304</v>
       </c>
       <c r="K119" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L119" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C120" t="s">
         <v>1437</v>
       </c>
-      <c r="B120" t="s">
+      <c r="D120" t="s">
         <v>1438</v>
       </c>
-      <c r="C120" t="s">
+      <c r="E120" t="s">
         <v>1439</v>
-      </c>
-      <c r="D120" t="s">
-        <v>1440</v>
-      </c>
-      <c r="E120" t="s">
-        <v>1441</v>
       </c>
       <c r="F120" t="n">
         <v>8</v>
@@ -39936,27 +39970,27 @@
         <v>6.11585</v>
       </c>
       <c r="K120" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L120" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B121" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D121" t="s">
         <v>1442</v>
       </c>
-      <c r="C121" t="s">
+      <c r="E121" t="s">
         <v>1443</v>
-      </c>
-      <c r="D121" t="s">
-        <v>1444</v>
-      </c>
-      <c r="E121" t="s">
-        <v>1445</v>
       </c>
       <c r="F121" t="n">
         <v>8</v>
@@ -39974,27 +40008,27 @@
         <v>6.11585</v>
       </c>
       <c r="K121" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L121" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B122" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D122" t="s">
         <v>1446</v>
       </c>
-      <c r="C122" t="s">
+      <c r="E122" t="s">
         <v>1447</v>
-      </c>
-      <c r="D122" t="s">
-        <v>1448</v>
-      </c>
-      <c r="E122" t="s">
-        <v>1449</v>
       </c>
       <c r="F122" t="n">
         <v>8</v>
@@ -40012,27 +40046,27 @@
         <v>6.11585</v>
       </c>
       <c r="K122" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L122" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C123" t="s">
         <v>1450</v>
       </c>
-      <c r="B123" t="s">
+      <c r="D123" t="s">
         <v>1451</v>
       </c>
-      <c r="C123" t="s">
+      <c r="E123" t="s">
         <v>1452</v>
-      </c>
-      <c r="D123" t="s">
-        <v>1453</v>
-      </c>
-      <c r="E123" t="s">
-        <v>1454</v>
       </c>
       <c r="F123"/>
       <c r="G123" t="n">
@@ -40048,27 +40082,27 @@
         <v>-38.0382</v>
       </c>
       <c r="K123" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L123" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B124" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D124" t="s">
+        <v>987</v>
+      </c>
+      <c r="E124" t="s">
         <v>1455</v>
-      </c>
-      <c r="C124" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D124" t="s">
-        <v>989</v>
-      </c>
-      <c r="E124" t="s">
-        <v>1457</v>
       </c>
       <c r="F124" t="n">
         <v>16</v>
@@ -40086,27 +40120,27 @@
         <v>14.5559</v>
       </c>
       <c r="K124" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L124" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B125" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D125" t="s">
+        <v>987</v>
+      </c>
+      <c r="E125" t="s">
         <v>1458</v>
-      </c>
-      <c r="C125" t="s">
-        <v>1459</v>
-      </c>
-      <c r="D125" t="s">
-        <v>989</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1460</v>
       </c>
       <c r="F125" t="n">
         <v>16</v>
@@ -40124,27 +40158,27 @@
         <v>14.5559</v>
       </c>
       <c r="K125" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L125" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B126" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D126" t="s">
+        <v>987</v>
+      </c>
+      <c r="E126" t="s">
         <v>1461</v>
-      </c>
-      <c r="C126" t="s">
-        <v>1462</v>
-      </c>
-      <c r="D126" t="s">
-        <v>989</v>
-      </c>
-      <c r="E126" t="s">
-        <v>1463</v>
       </c>
       <c r="F126"/>
       <c r="G126" t="n">
@@ -40160,27 +40194,27 @@
         <v>-26.596</v>
       </c>
       <c r="K126" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L126" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B127" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D127" t="s">
+        <v>987</v>
+      </c>
+      <c r="E127" t="s">
         <v>1464</v>
-      </c>
-      <c r="C127" t="s">
-        <v>1465</v>
-      </c>
-      <c r="D127" t="s">
-        <v>989</v>
-      </c>
-      <c r="E127" t="s">
-        <v>1466</v>
       </c>
       <c r="F127"/>
       <c r="G127" t="n">
@@ -40196,27 +40230,27 @@
         <v>-26.596</v>
       </c>
       <c r="K127" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L127" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B128" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D128" t="s">
+        <v>987</v>
+      </c>
+      <c r="E128" t="s">
         <v>1467</v>
-      </c>
-      <c r="C128" t="s">
-        <v>1468</v>
-      </c>
-      <c r="D128" t="s">
-        <v>989</v>
-      </c>
-      <c r="E128" t="s">
-        <v>1469</v>
       </c>
       <c r="F128"/>
       <c r="G128" t="n">
@@ -40232,27 +40266,27 @@
         <v>-26.596</v>
       </c>
       <c r="K128" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L128" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B129" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D129" t="s">
+        <v>987</v>
+      </c>
+      <c r="E129" t="s">
         <v>1470</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1471</v>
-      </c>
-      <c r="D129" t="s">
-        <v>989</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1472</v>
       </c>
       <c r="F129" t="n">
         <v>20</v>
@@ -40270,27 +40304,27 @@
         <v>-5.6681</v>
       </c>
       <c r="K129" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L129" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B130" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E130" t="s">
         <v>1473</v>
-      </c>
-      <c r="C130" t="s">
-        <v>1474</v>
-      </c>
-      <c r="D130" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E130" t="s">
-        <v>1475</v>
       </c>
       <c r="F130" t="n">
         <v>16</v>
@@ -40308,27 +40342,27 @@
         <v>13.7159</v>
       </c>
       <c r="K130" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="L130" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B131" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D131" t="s">
+        <v>987</v>
+      </c>
+      <c r="E131" t="s">
         <v>1476</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D131" t="s">
-        <v>989</v>
-      </c>
-      <c r="E131" t="s">
-        <v>1478</v>
       </c>
       <c r="F131" t="n">
         <v>19</v>
@@ -40346,27 +40380,27 @@
         <v>-18.4316</v>
       </c>
       <c r="K131" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L131" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B132" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D132" t="s">
+        <v>987</v>
+      </c>
+      <c r="E132" t="s">
         <v>1479</v>
-      </c>
-      <c r="C132" t="s">
-        <v>1480</v>
-      </c>
-      <c r="D132" t="s">
-        <v>989</v>
-      </c>
-      <c r="E132" t="s">
-        <v>1481</v>
       </c>
       <c r="F132" t="n">
         <v>19</v>
@@ -40384,27 +40418,27 @@
         <v>-18.4316</v>
       </c>
       <c r="K132" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="L132" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C133" t="s">
         <v>1482</v>
       </c>
-      <c r="B133" t="s">
+      <c r="D133" t="s">
         <v>1483</v>
       </c>
-      <c r="C133" t="s">
+      <c r="E133" t="s">
         <v>1484</v>
-      </c>
-      <c r="D133" t="s">
-        <v>1485</v>
-      </c>
-      <c r="E133" t="s">
-        <v>1486</v>
       </c>
       <c r="F133"/>
       <c r="G133" t="n">
@@ -40420,27 +40454,27 @@
         <v>-35.4415</v>
       </c>
       <c r="K133" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L133" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C134" t="s">
         <v>1487</v>
       </c>
-      <c r="B134" t="s">
+      <c r="D134" t="s">
         <v>1488</v>
       </c>
-      <c r="C134" t="s">
+      <c r="E134" t="s">
         <v>1489</v>
-      </c>
-      <c r="D134" t="s">
-        <v>1490</v>
-      </c>
-      <c r="E134" t="s">
-        <v>1491</v>
       </c>
       <c r="F134" t="n">
         <v>11</v>
@@ -40458,27 +40492,27 @@
         <v>-29.6233</v>
       </c>
       <c r="K134" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L134" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B135" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D135" t="s">
         <v>1492</v>
       </c>
-      <c r="C135" t="s">
+      <c r="E135" t="s">
         <v>1493</v>
-      </c>
-      <c r="D135" t="s">
-        <v>1494</v>
-      </c>
-      <c r="E135" t="s">
-        <v>1495</v>
       </c>
       <c r="F135" t="n">
         <v>11</v>
@@ -40496,27 +40530,27 @@
         <v>-29.6233</v>
       </c>
       <c r="K135" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L135" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C136" t="s">
         <v>1496</v>
       </c>
-      <c r="B136" t="s">
+      <c r="D136" t="s">
         <v>1497</v>
       </c>
-      <c r="C136" t="s">
+      <c r="E136" t="s">
         <v>1498</v>
-      </c>
-      <c r="D136" t="s">
-        <v>1499</v>
-      </c>
-      <c r="E136" t="s">
-        <v>1500</v>
       </c>
       <c r="F136"/>
       <c r="G136" t="n">
@@ -40532,27 +40566,27 @@
         <v>32.7196</v>
       </c>
       <c r="K136" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="L136" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B137" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D137" t="s">
+        <v>987</v>
+      </c>
+      <c r="E137" t="s">
         <v>1501</v>
-      </c>
-      <c r="C137" t="s">
-        <v>1502</v>
-      </c>
-      <c r="D137" t="s">
-        <v>989</v>
-      </c>
-      <c r="E137" t="s">
-        <v>1503</v>
       </c>
       <c r="F137" t="n">
         <v>19</v>
@@ -40570,10 +40604,10 @@
         <v>16.535</v>
       </c>
       <c r="K137" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="L137" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
   </sheetData>
@@ -40594,21 +40628,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1504</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="B2" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="C2" t="n">
         <v>0.000241136</v>
@@ -40616,10 +40650,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="B3" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="C3" t="n">
         <v>0.000892973</v>
@@ -40627,10 +40661,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B4" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="C4" t="n">
         <v>0.066469</v>
@@ -40638,10 +40672,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B5" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="C5" t="n">
         <v>0.0194887</v>
@@ -40649,10 +40683,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B6" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C6" t="n">
         <v>0.0109944</v>
@@ -40660,10 +40694,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B7" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C7" t="n">
         <v>0.00813665</v>
@@ -40671,10 +40705,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B8" t="s">
         <v>1517</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1519</v>
       </c>
       <c r="C8" t="n">
         <v>0.0635838</v>
@@ -40682,10 +40716,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="B9" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C9" t="n">
         <v>0.00307552</v>
@@ -40693,10 +40727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="B10" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C10" t="n">
         <v>0.000428907</v>
@@ -40704,10 +40738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="B11" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="C11" t="n">
         <v>0.0064538</v>
@@ -40715,10 +40749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="B12" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="C12" t="n">
         <v>0.0477691</v>
@@ -40726,10 +40760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="B13" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="C13" t="n">
         <v>0.0299564</v>
@@ -40737,10 +40771,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="B14" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C14" t="n">
         <v>0.0314322</v>
@@ -40748,10 +40782,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="B15" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="C15" t="n">
         <v>0.402813</v>
@@ -40759,10 +40793,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="B16" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="C16" t="n">
         <v>0.119695</v>
@@ -40770,10 +40804,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B17" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="C17" t="n">
         <v>0.276095</v>
@@ -40781,10 +40815,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B18" t="s">
         <v>1536</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1538</v>
       </c>
       <c r="C18" t="n">
         <v>0.00234262</v>
@@ -40792,10 +40826,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B19" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="C19" t="n">
         <v>0.0106935</v>
@@ -40803,10 +40837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B20" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C20" t="n">
         <v>0.0260947</v>
@@ -40814,10 +40848,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B21" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="C21" t="n">
         <v>0.38182</v>
@@ -40825,10 +40859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B22" t="s">
         <v>1543</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1545</v>
       </c>
       <c r="C22" t="n">
         <v>0.348605</v>
@@ -40836,10 +40870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B23" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="C23" t="n">
         <v>0.191683</v>
